--- a/artfynd/A 55653-2025 artfynd.xlsx
+++ b/artfynd/A 55653-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128340188</v>
+        <v>128532908</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713851</v>
+        <v>713850</v>
       </c>
       <c r="R2" t="n">
-        <v>7303401</v>
+        <v>7303293</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340189</v>
+        <v>128340186</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713853</v>
+        <v>713777</v>
       </c>
       <c r="R3" t="n">
-        <v>7303408</v>
+        <v>7303411</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340186</v>
+        <v>128340187</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713777</v>
+        <v>713797</v>
       </c>
       <c r="R4" t="n">
-        <v>7303411</v>
+        <v>7303417</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340187</v>
+        <v>128340188</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713797</v>
+        <v>713851</v>
       </c>
       <c r="R5" t="n">
-        <v>7303417</v>
+        <v>7303401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532907</v>
+        <v>128340189</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>714091</v>
+        <v>713853</v>
       </c>
       <c r="R6" t="n">
-        <v>7303182</v>
+        <v>7303408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,6 +1202,218 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128340204</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lomträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>713854</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7303261</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128532907</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lomträsk, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>714091</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7303182</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55653-2025 artfynd.xlsx
+++ b/artfynd/A 55653-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340189</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532907</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>